--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202608/Currency_P&L_20260819.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202608/Currency_P&L_20260819.xlsx
@@ -2381,37 +2381,37 @@
         <v>46253</v>
       </c>
       <c r="B55">
-        <v>94261905.13</v>
+        <v>93321892.78</v>
       </c>
       <c r="C55">
-        <v>5092.71</v>
+        <v>49310.01</v>
       </c>
       <c r="D55">
-        <v>5.4E-05</v>
+        <v>0.000523</v>
       </c>
       <c r="E55">
-        <v>-65353.35</v>
+        <v>-60837.97</v>
       </c>
       <c r="F55">
-        <v>-0.000693</v>
+        <v>-0.000645</v>
       </c>
       <c r="G55">
-        <v>-22858.71</v>
+        <v>-30731.42</v>
       </c>
       <c r="H55">
-        <v>-0.000243</v>
+        <v>-0.000326</v>
       </c>
       <c r="I55">
-        <v>-2816031.05</v>
+        <v>-833794.13</v>
       </c>
       <c r="J55">
-        <v>-0.029875</v>
+        <v>-0.008846</v>
       </c>
       <c r="M55">
-        <v>-13486.68</v>
+        <v>-24376.4</v>
       </c>
       <c r="N55">
-        <v>-0.000143</v>
+        <v>-0.000259</v>
       </c>
     </row>
   </sheetData>
